--- a/human_validation/judge/kor/judge_D019_S003_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S003_P003__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B42"/>
+  <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,145 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 병원에는 어떤 일로 오셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 사촌이 죽은 뒤로 제 수면이 정말 많이 바뀌어서 왔어요. 평소에는 수면에 대해 굉장히 철저한 편인데, 지금은 그날 밤을 계속 되새기느라 잠을 못 자고 누워 있어요. 그러다 새벽 3~4시쯤 병원의 단편적인 장면들과 함께 깨고요. 그러고 나서 이사회 회의에 들어가는데, 잠을 조각조각 잔 것 같은 느낌이에요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 사촌분이 돌아가신 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 한 3주 정도 됐어요, 사촌이 고속도로 충돌 사고로 죽은 그날 밤부터요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 충돌 사고나 병원을 떠올리게 하는 생각, 대화, 장소를 일부러 피하고 계신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 일부러 피한다고까지는 말 못 할 것 같아요. 제가 그러고 있다는 걸 딱히 느낀 적이 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 수면 문제 외에, 대부분의 날에 지속적으로 기분이 가라앉거나 우울하다고 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 대부분의 날에 기분이 가라앉았다고는 못 느낀 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 사고 이후로 평소와 다르게 예민해지거나 긴장되거나 쉽게 놀라는 느낌을 받으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네, 주로 운전할 때요. 계속 백미러를 확인하고, 주변 트럭들의 속도를 살피고, 어디로 빠져나갈 수 있을지 생각하게 돼요. 평소 사무실 가는 길에서도 몸이 계속 긴장돼 있어요, 마치 뭔가 일어나기를 기다리고 있는 것처럼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이 일이 있은 후로 감정적으로 무뎌지거나 다른 사람들과 거리감이 느껴지셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네, 그런 것 같아요. 추모 모임에서나 조카들이 저를 위로하려고 할 때, 겉으로는 평소처럼 행동했지만 속으로는 아무런 따뜻함이나 안도감이 느껴지지 않았어요. 마치 제 안의 다정한 부분이 그냥 조용해져 버린 것 같았어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>진단명: 급성 스트레스장애 (D019)
 인구통계: 성별 여성 / 나이 58 / 직업상태 chief executive / 최종학력 학사
@@ -575,194 +705,37 @@
 증상 지속 기간: 3 weeks
 추가 요건: 
 주호소 증상 코드: S027
-배경 서술: 헤탈벤의 사촌 동생은 어린 시절 그녀에게 친자매나 다름없었고, 같은 구자라트 커뮤니티 네트워크에서도 함께 활발히 활동해 온 사이였다. 그런 사촌이 둘이 함께 참석했던 문화협회 행사 후 귀가하던 중 고속도로 충돌 사고로 갑작스럽게 세상을 떠났다. 헤탈벤은 친척들에게 부고를 알리고 장례식 일부를 조율하는 책임을 맡았지만, 경찰 통화와 병원 방문 당시의 일부 기억을 제대로 재구성하지 못하는 자신을 발견했고, 평소 정확한 통제력과 기억력에 익숙했던 그녀에게 이는 매우 혼란스러운 일이었다. 이후 3주 동안 그녀는 필수적인 임원 회의에는 계속 참석했지만, 수면 장애, 병원 복도의 단편적인 기억이 불쑥 떠오르는 증상, 가족 의식 중 감정이 무뎌지는 느낌, 리더십 팀에 대한 짜증, 그리고 운전 중 지나친 경계심이 그녀의 업무와 지역사회 활동에 지장을 주기 시작했다. 결국 그녀는 STEM 멘토링 세션 도중 평정심을 잃은 뒤, 규칙적인 생활 습관과 요가, 명상만으로는 더 이상 자신을 지탱할 수 없다는 것을 깨닫고 직접 정신과에 연락했다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요. 오늘 병원에는 어떤 일로 오셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 사촌이 죽은 뒤로 제 수면이 정말 많이 바뀌어서 왔어요. 평소에는 수면에 대해 굉장히 철저한 편인데, 지금은 그날 밤을 계속 되새기느라 잠을 못 자고 누워 있어요. 그러다 새벽 3~4시쯤 병원의 단편적인 장면들과 함께 깨고요. 그러고 나서 이사회 회의에 들어가는데, 잠을 조각조각 잔 것 같은 느낌이에요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 사촌분이 돌아가신 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 한 3주 정도 됐어요, 사촌이 고속도로 충돌 사고로 죽은 그날 밤부터요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 충돌 사고나 병원을 떠올리게 하는 생각, 대화, 장소를 일부러 피하고 계신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 일부러 피한다고까지는 말 못 할 것 같아요. 제가 그러고 있다는 걸 딱히 느낀 적이 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 수면 문제 외에, 대부분의 날에 지속적으로 기분이 가라앉거나 우울하다고 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 잘 모르겠어요. 대부분의 날에 기분이 가라앉았다고는 못 느낀 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 사고 이후로 평소와 다르게 예민해지거나 긴장되거나 쉽게 놀라는 느낌을 받으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네, 주로 운전할 때요. 계속 백미러를 확인하고, 주변 트럭들의 속도를 살피고, 어디로 빠져나갈 수 있을지 생각하게 돼요. 평소 사무실 가는 길에서도 몸이 계속 긴장돼 있어요, 마치 뭔가 일어나기를 기다리고 있는 것처럼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이 일이 있은 후로 감정적으로 무뎌지거나 다른 사람들과 거리감이 느껴지셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네, 그런 것 같아요. 추모 모임에서나 조카들이 저를 위로하려고 할 때, 겉으로는 평소처럼 행동했지만 속으로는 아무런 따뜻함이나 안도감이 느껴지지 않았어요. 마치 제 안의 다정한 부분이 그냥 조용해져 버린 것 같았어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
+배경 서술: 헤탈벤의 사촌 동생은 어린 시절 그녀에게 친자매나 다름없었고, 같은 구자라트 커뮤니티 네트워크에서도 함께 활발히 활동해 온 사이였다. 그런 사촌이 둘이 함께 참석했던 문화협회 행사 후 귀가하던 중 고속도로 충돌 사고로 갑작스럽게 세상을 떠났다. 헤탈벤은 친척들에게 부고를 알리고 장례식 일부를 조율하는 책임을 맡았지만, 경찰 통화와 병원 방문 당시의 일부 기억을 제대로 재구성하지 못하는 자신을 발견했고, 평소 정확한 통제력과 기억력에 익숙했던 그녀에게 이는 매우 혼란스러운 일이었다. 이후 3주 동안 그녀는 필수적인 임원 회의에는 계속 참석했지만, 수면 장애, 병원 복도의 단편적인 기억이 불쑥 떠오르는 증상, 가족 의식 중 감정이 무뎌지는 느낌, 리더십 팀에 대한 짜증, 그리고 운전 중 지나친 경계심이 그녀의 업무와 지역사회 활동에 지장을 주기 시작했다. 결국 그녀는 STEM 멘토링 세션 도중 평정심을 잃은 뒤, 규칙적인 생활 습관과 요가, 명상만으로는 더 이상 자신을 지탱할 수 없다는 것을 깨닫고 직접 정신과에 연락했다.
+표집된 증상 목록:
+  - S027 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - S069 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - S071 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).
+  - S076 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).
+  - S077 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.
+  - S079 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.</t>
+        </is>
+      </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>[6번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 범불안장애 (D011); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018); 급성 스트레스장애 (D019) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 급성 스트레스장애 (D019, ICD: F43.0)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: acute_stress_symptoms (관계=must_include, 요구개수=6, 충족개수=4, 커버리지=0.6667)
-  확인된 근거: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.; 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).; 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.
-  누락: 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.; 외상 관련 회피: 외상 사건과 관련된 자극을 지속적으로 회피함.; 외상 관련 기억상실: 외상 사건의 중요한 부분을 기억하지 못함(통상 해리성 기억상실에 의한 것으로, 두부 손상이나 알코올 등 다른 요인에 의한 것이 아님).; 과민성/공격성: 사소하거나 별다른 도발 없이도 언어적·신체적 공격성으로 나타나는 과민한 행동과 분노 폭발.; 과장된 놀람 반응: 사소한 자극에도 과장되게 놀라는 반응.; 이인증/비현실감: 외상 사건 이후 자기 자신이나 주변 환경에 대한 현실감이 변화된 상태.</t>
+          <t>의사의 최종 진단: 급성 스트레스장애 (D019, ICD: F43.0)
+지속 기간 요건: 있음
+기능적 손상 요건: 있음
+추가 요건: None
+체크리스트 그룹: acute_stress_symptoms (관계=must_include, 요구개수=6, 충족개수=4, 커버리지=0.6667)
+확인된 근거:
+  - 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.
+  - 침투 증상: 외상 사건에 대한 반복적이고 비자발적이며 침투적인 고통스러운 기억.
+  - 긍정적 정서 표현 불능: 긍정적 정서를 지속적으로 경험하지 못함(예: 행복, 만족, 애정을 느끼지 못함).
+  - 과각성: 주변 환경에 대해 지속적으로 경계하고 긴장하는 상태.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D019_S003_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S003_P003__gemini-3.8-flash_kor.xlsx
@@ -691,6 +691,11 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -731,11 +736,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D019_S003_P003__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D019_S003_P003__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1401</v>
+        <v>0.1875</v>
       </c>
     </row>
     <row r="5">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1515</v>
+        <v>0.2083</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.9333</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.75</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
